--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>480.92</v>
+        <v>478.45</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>820.35</v>
+        <v>812.16</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>62089.78</v>
+        <v>61470.12</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12396.63</v>
+        <v>12266.81</v>
       </c>
     </row>
     <row r="6">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12680.38</v>
+        <v>12611.07</v>
       </c>
     </row>
     <row r="7">
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3848.21</v>
+        <v>3827.18</v>
       </c>
     </row>
     <row r="8">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>300.31</v>
+        <v>298.67</v>
       </c>
     </row>
     <row r="9">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12371.25</v>
+        <v>12415.4</v>
       </c>
     </row>
     <row r="10">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13300.24</v>
+        <v>13347.7</v>
       </c>
     </row>
     <row r="11">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>36920.85</v>
+        <v>37052.62</v>
       </c>
     </row>
     <row r="12">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>467.03</v>
+        <v>468.7</v>
       </c>
     </row>
     <row r="13">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7279.6</v>
+        <v>7305.58</v>
       </c>
     </row>
     <row r="14">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7751.7</v>
+        <v>7777.2</v>
       </c>
     </row>
     <row r="15">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3622.97</v>
+        <v>3634.88</v>
       </c>
     </row>
     <row r="16">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>801.54</v>
+        <v>804.1799999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4761.69</v>
+        <v>4783.87</v>
       </c>
     </row>
     <row r="18">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2642.68</v>
+        <v>2631.79</v>
       </c>
     </row>
     <row r="19">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6861.19</v>
+        <v>6850.56</v>
       </c>
     </row>
     <row r="20">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3505.41</v>
+        <v>3499.97</v>
       </c>
     </row>
     <row r="21">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>639.63</v>
+        <v>638.64</v>
       </c>
     </row>
     <row r="22">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>34509.71</v>
+        <v>34456.23</v>
       </c>
     </row>
     <row r="23">
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12824.66</v>
+        <v>12890.89</v>
       </c>
     </row>
     <row r="24">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9503.07</v>
+        <v>9552.15</v>
       </c>
     </row>
     <row r="25">
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>17840.09</v>
+        <v>17932.22</v>
       </c>
     </row>
     <row r="26">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4832.76</v>
+        <v>4866.87</v>
       </c>
     </row>
     <row r="27">
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>683.98</v>
+        <v>688.8099999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3798.45</v>
+        <v>3760.66</v>
       </c>
     </row>
     <row r="29">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>37.33</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="30">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>124.43</v>
+        <v>123.19</v>
       </c>
     </row>
     <row r="31">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10789.29</v>
+        <v>10681.94</v>
       </c>
     </row>
     <row r="32">
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12699.7</v>
+        <v>12672.22</v>
       </c>
     </row>
     <row r="33">
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>57015.78</v>
+        <v>56892.39</v>
       </c>
     </row>
     <row r="34">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6387.51</v>
+        <v>6360.73</v>
       </c>
     </row>
     <row r="35">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1702.75</v>
+        <v>1695.61</v>
       </c>
     </row>
     <row r="36">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7460.74</v>
+        <v>7397.54</v>
       </c>
     </row>
     <row r="37">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>33985.49</v>
+        <v>33958.17</v>
       </c>
     </row>
     <row r="38">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>948.79</v>
+        <v>948.03</v>
       </c>
     </row>
     <row r="39">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12650.59</v>
+        <v>12699.14</v>
       </c>
     </row>
     <row r="40">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7051.15</v>
+        <v>7078.21</v>
       </c>
     </row>
     <row r="41">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11523.52</v>
+        <v>11567.75</v>
       </c>
     </row>
     <row r="42">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18939.07</v>
+        <v>18989.29</v>
       </c>
     </row>
     <row r="43">
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4489.92</v>
+        <v>4483.62</v>
       </c>
     </row>
     <row r="44">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3623.81</v>
+        <v>3648.75</v>
       </c>
     </row>
     <row r="45">
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10047.88</v>
+        <v>10117.05</v>
       </c>
     </row>
     <row r="46">
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>873.21</v>
+        <v>879.22</v>
       </c>
     </row>
     <row r="47">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13098.11</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="48">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>35245.53</v>
+        <v>35546.73</v>
       </c>
     </row>
     <row r="49">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>103.69</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="50">
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12961.67</v>
+        <v>13032.55</v>
       </c>
     </row>
     <row r="51">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>52354.12</v>
+        <v>51603.72</v>
       </c>
     </row>
     <row r="52">
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12810.45</v>
+        <v>12828.24</v>
       </c>
     </row>
     <row r="53">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>37958.49</v>
+        <v>38011.19</v>
       </c>
     </row>
     <row r="54">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7646.51</v>
+        <v>7657.12</v>
       </c>
     </row>
     <row r="55">
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11902.33</v>
+        <v>11894.2</v>
       </c>
     </row>
     <row r="56">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8291.33</v>
+        <v>8262.870000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4841.82</v>
+        <v>4816.24</v>
       </c>
     </row>
     <row r="58">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3750.71</v>
+        <v>3730.9</v>
       </c>
     </row>
     <row r="59">
@@ -4034,13 +4034,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5115.58</v>
+        <v>5184.47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1274667-2-CM26</t>
+          <t>418-112-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>13575.19</v>
+        <v>37417.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3951-9-CM26</t>
+          <t>3951-10-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1149.93</v>
+        <v>7410.83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3951-10-CM26</t>
+          <t>1274667-2-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4217,13 +4217,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7234.9</v>
+        <v>13905.31</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>418-112-CM26</t>
+          <t>3951-9-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>36529.3</v>
+        <v>1177.9</v>
       </c>
     </row>
     <row r="64">
@@ -4339,7 +4339,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>271.5</v>
+        <v>279.74</v>
       </c>
     </row>
     <row r="65">
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2542.86</v>
+        <v>2550.23</v>
       </c>
     </row>
     <row r="66">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>66777.83</v>
+        <v>67122.78</v>
       </c>
     </row>
     <row r="67">
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13172.4</v>
+        <v>13116.86</v>
       </c>
     </row>
     <row r="68">
@@ -4583,13 +4583,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>25222.36</v>
+        <v>25291.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>655348-11-CM26</t>
+          <t>1274667-31-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>401.96</v>
+        <v>15804.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1274667-31-CM26</t>
+          <t>655348-11-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>15695.69</v>
+        <v>404.76</v>
       </c>
     </row>
     <row r="71">
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>37113.61</v>
+        <v>37444.17</v>
       </c>
     </row>
     <row r="72">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>14157.1</v>
+        <v>14283.19</v>
       </c>
     </row>
     <row r="73">
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11617.94</v>
+        <v>11721.42</v>
       </c>
     </row>
     <row r="74">
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11681.86</v>
+        <v>11785.91</v>
       </c>
     </row>
     <row r="75">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>104.7</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="76">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1160.07</v>
+        <v>1151.75</v>
       </c>
     </row>
     <row r="77">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9310.219999999999</v>
+        <v>9259.52</v>
       </c>
     </row>
     <row r="78">
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>37459.28</v>
+        <v>37238.53</v>
       </c>
     </row>
     <row r="79">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3658.85</v>
+        <v>3636.61</v>
       </c>
     </row>
     <row r="80">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10237.61</v>
+        <v>10198.1</v>
       </c>
     </row>
     <row r="81">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5418.25</v>
+        <v>5507.55</v>
       </c>
     </row>
     <row r="82">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>51612.98</v>
+        <v>51739.97</v>
       </c>
     </row>
     <row r="83">
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11526.63</v>
+        <v>11445.28</v>
       </c>
     </row>
     <row r="84">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>22157.44</v>
+        <v>22504.52</v>
       </c>
     </row>
     <row r="85">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4969.81</v>
+        <v>4969.56</v>
       </c>
     </row>
     <row r="86">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9559.58</v>
+        <v>9559.09</v>
       </c>
     </row>
     <row r="87">
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>34046.88</v>
+        <v>34045.13</v>
       </c>
     </row>
     <row r="88">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>11827.32</v>
+        <v>11826.71</v>
       </c>
     </row>
     <row r="89">
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2429.05</v>
+        <v>2418.19</v>
       </c>
     </row>
     <row r="90">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>867.11</v>
+        <v>863.23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3765-246-CM26</t>
+          <t>3949-116-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>9973.040000000001</v>
+        <v>8203.540000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3949-116-CM26</t>
+          <t>3765-246-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6047,7 +6047,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8240.389999999999</v>
+        <v>9928.450000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14869.88</v>
+        <v>14882.69</v>
       </c>
     </row>
     <row r="94">
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>36083.47</v>
+        <v>35545.27</v>
       </c>
     </row>
     <row r="95">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9957.379999999999</v>
+        <v>9813.32</v>
       </c>
     </row>
     <row r="96">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>15068.73</v>
+        <v>14671.92</v>
       </c>
     </row>
     <row r="97">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>69912.14999999999</v>
+        <v>68071.13</v>
       </c>
     </row>
     <row r="98">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>38016.98</v>
+        <v>37953.42</v>
       </c>
     </row>
     <row r="99">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12828.74</v>
+        <v>12807.29</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1079689-141-CM26</t>
+          <t>2151-119-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>26268.5</v>
+        <v>9671.219999999999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3950-487-CM26</t>
+          <t>1079689-141-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6561,17 +6561,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6596,13 +6596,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5206.62</v>
+        <v>26224.58</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2151-119-CM26</t>
+          <t>3950-487-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6622,17 +6622,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9687.42</v>
+        <v>5197.91</v>
       </c>
     </row>
     <row r="103">
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3697.57</v>
+        <v>3746.8</v>
       </c>
     </row>
     <row r="104">
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>13953.44</v>
+        <v>14139.2</v>
       </c>
     </row>
     <row r="105">
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15711.9</v>
+        <v>15921.07</v>
       </c>
     </row>
     <row r="106">
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>11585.54</v>
+        <v>11739.78</v>
       </c>
     </row>
     <row r="107">
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>389.8</v>
+        <v>394.89</v>
       </c>
     </row>
     <row r="108">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3512.69</v>
+        <v>3599.14</v>
       </c>
     </row>
     <row r="109">
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10311.66</v>
+        <v>10333.02</v>
       </c>
     </row>
     <row r="110">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>69611.34</v>
+        <v>68664.92999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>22617.7</v>
+        <v>22310.19</v>
       </c>
     </row>
     <row r="112">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4785.78</v>
+        <v>4811.55</v>
       </c>
     </row>
     <row r="113">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16510</v>
+        <v>16598.9</v>
       </c>
     </row>
     <row r="114">
@@ -7389,7 +7389,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3894.21</v>
+        <v>3923.71</v>
       </c>
     </row>
     <row r="115">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6301.85</v>
+        <v>6285.93</v>
       </c>
     </row>
     <row r="116">
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>39983.3</v>
+        <v>40363.17</v>
       </c>
     </row>
     <row r="117">
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>15220.95</v>
+        <v>15365.56</v>
       </c>
     </row>
     <row r="118">
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3038.47</v>
+        <v>3061.11</v>
       </c>
     </row>
     <row r="119">
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>13271.5</v>
+        <v>13370.37</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3950-689-CM26</t>
+          <t>2151-165-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>13417.02</v>
+        <v>8885.860000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>987.38</v>
+        <v>994.73</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2151-165-CM26</t>
+          <t>3950-689-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8820.15</v>
+        <v>13516.97</v>
       </c>
     </row>
     <row r="123">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>11747.5</v>
+        <v>11630.34</v>
       </c>
     </row>
     <row r="124">
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>36987.08</v>
+        <v>37168.77</v>
       </c>
     </row>
     <row r="125">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12153.9</v>
+        <v>12194.22</v>
       </c>
     </row>
     <row r="126">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>24708.42</v>
+        <v>25126.3</v>
       </c>
     </row>
     <row r="127">
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>61840.46</v>
+        <v>61371.32</v>
       </c>
     </row>
     <row r="128">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>5005.62</v>
+        <v>4921.05</v>
       </c>
     </row>
     <row r="129">
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>11701.69</v>
+        <v>11535.62</v>
       </c>
     </row>
     <row r="130">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5840.07</v>
+        <v>5757.18</v>
       </c>
     </row>
     <row r="131">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>13729.71</v>
+        <v>13541.06</v>
       </c>
     </row>
     <row r="132">
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9420.24</v>
+        <v>9290.809999999999</v>
       </c>
     </row>
     <row r="133">
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>14977.02</v>
+        <v>15045.04</v>
       </c>
     </row>
     <row r="134">
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>10514.96</v>
+        <v>10562.72</v>
       </c>
     </row>
     <row r="135">
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>37571.61</v>
+        <v>37742.24</v>
       </c>
     </row>
     <row r="136">
@@ -8731,7 +8731,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4204.83</v>
+        <v>4223.92</v>
       </c>
     </row>
     <row r="137">
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10253.11</v>
+        <v>10448.04</v>
       </c>
     </row>
     <row r="138">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4029.29</v>
+        <v>4120.16</v>
       </c>
     </row>
     <row r="139">
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>38530.11</v>
+        <v>37775.93</v>
       </c>
     </row>
     <row r="140">
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>12577.28</v>
+        <v>12390.94</v>
       </c>
     </row>
     <row r="141">
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24382.36</v>
+        <v>24626.52</v>
       </c>
     </row>
     <row r="142">
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>68410.63</v>
+        <v>68759.23</v>
       </c>
     </row>
     <row r="143">
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10017.17</v>
+        <v>10038.52</v>
       </c>
     </row>
     <row r="144">
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>15069.96</v>
+        <v>15168.21</v>
       </c>
     </row>
     <row r="145">
@@ -9280,13 +9280,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>42374.52</v>
+        <v>42471.7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3949-287-CM26</t>
+          <t>1274667-257-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9341,13 +9341,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>16460</v>
+        <v>14598.07</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>655348-64-CM26</t>
+          <t>3949-287-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9402,13 +9402,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>386.69</v>
+        <v>16570.18</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1274667-257-CM26</t>
+          <t>655348-64-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9463,13 +9463,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>14501</v>
+        <v>389.28</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1079689-299-CM26</t>
+          <t>3950-1047-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>25810.31</v>
+        <v>14044.37</v>
       </c>
     </row>
     <row r="150">
@@ -9585,13 +9585,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12436.19</v>
+        <v>12523.22</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>3950-1047-CM26</t>
+          <t>1079689-299-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>13946.76</v>
+        <v>25990.94</v>
       </c>
     </row>
     <row r="152">
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5467.02</v>
+        <v>5449.75</v>
       </c>
     </row>
     <row r="153">
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>347.38</v>
+        <v>346.28</v>
       </c>
     </row>
     <row r="154">
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>12135.13</v>
+        <v>12110.8</v>
       </c>
     </row>
     <row r="155">
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5112.95</v>
+        <v>5102.7</v>
       </c>
     </row>
     <row r="156">
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3831.7</v>
+        <v>3809.52</v>
       </c>
     </row>
     <row r="157">
@@ -10012,7 +10012,129 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>37388.42</v>
+        <v>36953.38</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3949-329-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>13759.22</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1274667-318-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>14672.71</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M159"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5019-2201-CM25</t>
+          <t>707426-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>478.45</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079689-357-CM25</t>
+          <t>3949-11-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>812.16</v>
+        <v>8317.950000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1691-3109-CM25</t>
+          <t>1079689-39-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>61470.12</v>
+        <v>19695.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3950-4667-CM25</t>
+          <t>3949-70-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12266.81</v>
+        <v>11583.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>951405-367-CM25</t>
+          <t>2151-46-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,10 +783,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12611.07</v>
+        <v>7126.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>951405-370-CM25</t>
+          <t>1692-172-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -825,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -840,10 +844,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -866,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3827.18</v>
+        <v>10052.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1154-53-CM25</t>
+          <t>1692-2425-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -882,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -927,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>298.67</v>
+        <v>11008.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1692-2969-CM25</t>
+          <t>1692-2586-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -943,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -988,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12415.4</v>
+        <v>11931.31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3949-399-CM25</t>
+          <t>1692-2667-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1004,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1019,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1049,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13347.7</v>
+        <v>11859.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>734-1133-CM25</t>
+          <t>1079689-232-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1065,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1080,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1110,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37052.62</v>
+        <v>18110.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3431-174-CM25</t>
+          <t>3949-305-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1126,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1141,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1171,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>468.7</v>
+        <v>11046.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2151-393-CM25</t>
+          <t>1403-4067-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1187,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1202,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1232,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7305.58</v>
+        <v>519.48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3765-830-CM25</t>
+          <t>2151-322-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1248,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1263,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1293,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7777.2</v>
+        <v>7321.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1154-57-CM25</t>
+          <t>3949-345-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1309,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1354,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3634.88</v>
+        <v>11487.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1154-58-CM25</t>
+          <t>1692-2873-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1370,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1415,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>804.1799999999999</v>
+        <v>10784.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3950-4755-CM25</t>
+          <t>655348-88-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1431,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1476,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4783.87</v>
+        <v>5372.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4067-28-CM25</t>
+          <t>5019-2201-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1497,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1537,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2631.79</v>
+        <v>478.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>697209-45-CM25</t>
+          <t>1079689-357-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1558,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1598,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6850.56</v>
+        <v>812.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3431-179-CM25</t>
+          <t>1691-3109-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1619,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1629,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1659,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3499.97</v>
+        <v>61470.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079689-385-CM25</t>
+          <t>3950-4667-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1680,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1720,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>638.64</v>
+        <v>12266.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>418-7259-CM25</t>
+          <t>951405-367-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1741,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1751,14 +1759,10 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
-        </is>
-      </c>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -1781,13 +1785,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>34456.23</v>
+        <v>12611.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1274667-648-CM25</t>
+          <t>951405-370-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1802,7 +1806,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1812,14 +1816,10 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
-        </is>
-      </c>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12890.89</v>
+        <v>3827.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3951-384-CM25</t>
+          <t>1154-53-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1863,22 +1863,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9552.15</v>
+        <v>298.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079689-397-CM25</t>
+          <t>3431-174-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>17932.22</v>
+        <v>468.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3431-176-CM25</t>
+          <t>3949-399-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4866.87</v>
+        <v>13347.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>951405-389-CM25</t>
+          <t>734-1133-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2056,10 +2056,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -2082,13 +2086,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>688.8099999999999</v>
+        <v>37052.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>655348-105-CM25</t>
+          <t>1692-2969-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2098,12 +2102,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2113,12 +2117,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2143,13 +2147,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3760.66</v>
+        <v>12415.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1079689-403-CM25</t>
+          <t>2151-393-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2159,12 +2163,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2174,12 +2178,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2204,13 +2208,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>36.96</v>
+        <v>7305.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3951-397-CM25</t>
+          <t>3765-830-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2220,12 +2224,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2235,12 +2239,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2265,13 +2269,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>123.19</v>
+        <v>7777.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3950-4823-CM25</t>
+          <t>1154-58-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2281,12 +2285,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2296,12 +2300,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2326,13 +2330,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10681.94</v>
+        <v>804.1799999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>951405-391-CM25</t>
+          <t>1154-57-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2342,27 +2346,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2387,13 +2391,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>12672.22</v>
+        <v>3634.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1691-3476-CM25</t>
+          <t>3950-4755-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2403,27 +2407,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2448,13 +2452,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>56892.39</v>
+        <v>4783.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3431-178-CM25</t>
+          <t>4067-28-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2464,27 +2468,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2509,13 +2513,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6360.73</v>
+        <v>2631.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>655348-110-CM25</t>
+          <t>3431-179-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2525,12 +2529,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2540,7 +2544,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2570,13 +2574,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1695.61</v>
+        <v>3499.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2151-449-CM25</t>
+          <t>1079689-385-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2586,12 +2590,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2601,12 +2605,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2631,13 +2635,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7397.54</v>
+        <v>638.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>734-1196-CM25</t>
+          <t>418-7259-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2647,12 +2651,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2662,12 +2666,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2692,13 +2696,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>33958.17</v>
+        <v>34456.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079689-427-CM25</t>
+          <t>697209-45-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2708,27 +2712,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,13 +2757,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>948.03</v>
+        <v>6850.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3949-458-CM25</t>
+          <t>1079689-397-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2769,12 +2773,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2784,12 +2788,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2814,13 +2818,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12699.14</v>
+        <v>17932.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3765-918-CM25</t>
+          <t>1274667-648-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2830,12 +2834,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2845,12 +2849,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2875,13 +2879,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7078.21</v>
+        <v>12890.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1692-3022-CM25</t>
+          <t>3951-384-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2891,12 +2895,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2906,12 +2910,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2936,13 +2940,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11567.75</v>
+        <v>9552.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1079689-439-CM25</t>
+          <t>951405-389-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2952,12 +2956,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2967,14 +2971,10 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
-        </is>
-      </c>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18989.29</v>
+        <v>688.8099999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3950-4910-CM25</t>
+          <t>3431-176-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3013,27 +3013,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4483.62</v>
+        <v>4866.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>951405-406-CM25</t>
+          <t>655348-105-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3648.75</v>
+        <v>3760.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3951-428-CM25</t>
+          <t>1079689-403-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3180,13 +3180,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10117.05</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>951405-407-CM25</t>
+          <t>3950-4823-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3241,13 +3241,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>879.22</v>
+        <v>10681.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1274667-796-CM25</t>
+          <t>3951-397-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3302,13 +3302,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>13210.04</v>
+        <v>123.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>418-8932-CM25</t>
+          <t>1691-3476-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>35546.73</v>
+        <v>56892.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>707426-219-CM25</t>
+          <t>951405-391-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>104.97</v>
+        <v>12672.22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3949-479-CM25</t>
+          <t>3431-178-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13032.55</v>
+        <v>6360.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1691-16-CM26</t>
+          <t>655348-110-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>51603.72</v>
+        <v>1695.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3950-64-CM26</t>
+          <t>2151-449-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3562,27 +3562,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12828.24</v>
+        <v>7397.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>734-4-CM26</t>
+          <t>1079689-427-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3668,13 +3668,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>38011.19</v>
+        <v>948.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2151-4-CM26</t>
+          <t>734-1196-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7657.12</v>
+        <v>33958.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1692-14-CM26</t>
+          <t>3949-458-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11894.2</v>
+        <v>12699.14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3765-6-CM26</t>
+          <t>3765-918-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8262.870000000001</v>
+        <v>7078.21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3431-2-CM26</t>
+          <t>1692-3022-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3912,13 +3912,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4816.24</v>
+        <v>11567.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3950-82-CM26</t>
+          <t>1079689-439-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3928,27 +3928,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3973,13 +3973,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3730.9</v>
+        <v>18989.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3431-7-CM26</t>
+          <t>3950-4910-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3989,27 +3989,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4034,13 +4034,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5184.47</v>
+        <v>4483.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>418-112-CM26</t>
+          <t>951405-407-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>37417.61</v>
+        <v>879.22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3951-10-CM26</t>
+          <t>3951-428-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7410.83</v>
+        <v>10117.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1274667-2-CM26</t>
+          <t>951405-406-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4217,13 +4217,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>13905.31</v>
+        <v>3648.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3951-9-CM26</t>
+          <t>418-8932-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1177.9</v>
+        <v>35546.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3431-9-CM26</t>
+          <t>1274667-796-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4339,13 +4339,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>279.74</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>951405-28-CM26</t>
+          <t>707426-219-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4400,13 +4400,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2550.23</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1691-233-CM26</t>
+          <t>3949-479-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>67122.78</v>
+        <v>13032.55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3950-225-CM26</t>
+          <t>1691-16-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4477,27 +4477,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4522,13 +4522,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13116.86</v>
+        <v>51603.72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1079689-47-CM26</t>
+          <t>3950-64-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4538,27 +4538,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4583,13 +4583,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>25291.6</v>
+        <v>12828.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1274667-31-CM26</t>
+          <t>734-4-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>15804.97</v>
+        <v>38011.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>655348-11-CM26</t>
+          <t>2151-4-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>404.76</v>
+        <v>7657.12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>734-43-CM26</t>
+          <t>1692-14-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4721,12 +4721,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>37444.17</v>
+        <v>11894.2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1692-84-CM26</t>
+          <t>3765-6-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>14283.19</v>
+        <v>8262.870000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3765-153-CM26</t>
+          <t>3431-2-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4888,13 +4888,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11721.42</v>
+        <v>4816.24</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3949-53-CM26</t>
+          <t>3950-82-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4904,27 +4904,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4949,13 +4949,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11785.91</v>
+        <v>3730.9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3765-156-CM26</t>
+          <t>3431-7-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>104.52</v>
+        <v>5184.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>655348-16-CM26</t>
+          <t>1274667-2-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1151.75</v>
+        <v>13905.31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2151-41-CM26</t>
+          <t>3951-9-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9259.52</v>
+        <v>1177.9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>418-579-CM26</t>
+          <t>3951-10-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>37238.53</v>
+        <v>7410.83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>951405-36-CM26</t>
+          <t>418-112-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5254,13 +5254,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3636.61</v>
+        <v>37417.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3951-45-CM26</t>
+          <t>3431-9-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10198.1</v>
+        <v>279.74</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3950-335-CM26</t>
+          <t>951405-28-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5331,27 +5331,27 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5376,13 +5376,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>5507.55</v>
+        <v>2550.23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1691-448-CM26</t>
+          <t>1691-233-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>51739.97</v>
+        <v>67122.78</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3950-351-CM26</t>
+          <t>3950-225-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5498,13 +5498,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11445.28</v>
+        <v>13116.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1079689-89-CM26</t>
+          <t>1079689-47-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5559,13 +5559,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>22504.52</v>
+        <v>25291.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3431-38-CM26</t>
+          <t>1274667-31-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4969.56</v>
+        <v>15804.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2151-77-CM26</t>
+          <t>655348-11-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5681,13 +5681,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9559.09</v>
+        <v>404.76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>734-134-CM26</t>
+          <t>3949-53-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5742,13 +5742,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>34045.13</v>
+        <v>11785.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1692-163-CM26</t>
+          <t>3765-153-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5803,13 +5803,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>11826.71</v>
+        <v>11721.42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1179784-4-CM26</t>
+          <t>1692-84-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5864,13 +5864,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2418.19</v>
+        <v>14283.19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1294237-17-CM26</t>
+          <t>734-43-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>863.23</v>
+        <v>37444.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3949-116-CM26</t>
+          <t>3765-156-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8203.540000000001</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3765-246-CM26</t>
+          <t>655348-16-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>9928.450000000001</v>
+        <v>1151.75</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1274667-107-CM26</t>
+          <t>2151-41-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6108,13 +6108,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14882.69</v>
+        <v>9259.52</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>418-935-CM26</t>
+          <t>418-579-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6169,13 +6169,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>35545.27</v>
+        <v>37238.53</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3951-61-CM26</t>
+          <t>951405-36-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6230,13 +6230,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9813.32</v>
+        <v>3636.61</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1274667-138-CM26</t>
+          <t>3951-45-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>14671.92</v>
+        <v>10198.1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4778-151-CM26</t>
+          <t>3950-335-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6307,27 +6307,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6352,13 +6352,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>68071.13</v>
+        <v>5507.55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>734-209-CM26</t>
+          <t>1691-448-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6413,13 +6413,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>37953.42</v>
+        <v>51739.97</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3950-533-CM26</t>
+          <t>3950-351-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>12807.29</v>
+        <v>11445.28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2151-119-CM26</t>
+          <t>1079689-89-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>9671.219999999999</v>
+        <v>22504.52</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1079689-141-CM26</t>
+          <t>3431-38-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6596,13 +6596,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>26224.58</v>
+        <v>4969.56</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3950-487-CM26</t>
+          <t>2151-77-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6612,27 +6612,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6657,13 +6657,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5197.91</v>
+        <v>9559.09</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3431-49-CM26</t>
+          <t>734-134-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6718,13 +6718,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3746.8</v>
+        <v>34045.13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1692-258-CM26</t>
+          <t>1692-163-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6779,13 +6779,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>14139.2</v>
+        <v>11826.71</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3949-161-CM26</t>
+          <t>3765-246-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6840,13 +6840,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15921.07</v>
+        <v>9928.450000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3765-328-CM26</t>
+          <t>3949-116-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>11739.78</v>
+        <v>8203.540000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1403-272-CM26</t>
+          <t>1294237-17-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6962,13 +6962,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>394.89</v>
+        <v>863.23</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>951405-100-CM26</t>
+          <t>1179784-4-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7023,13 +7023,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3599.14</v>
+        <v>2418.19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3951-90-CM26</t>
+          <t>1274667-107-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7054,12 +7054,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7084,13 +7084,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10333.02</v>
+        <v>14882.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>4778-256-CM26</t>
+          <t>418-935-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7145,13 +7145,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>68664.92999999999</v>
+        <v>35545.27</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1079689-170-CM26</t>
+          <t>3951-61-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7206,13 +7206,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>22310.19</v>
+        <v>9813.32</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3431-61-CM26</t>
+          <t>1274667-138-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7267,13 +7267,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4811.55</v>
+        <v>14671.92</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>707426-69-CM26</t>
+          <t>4778-151-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7328,13 +7328,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>16598.9</v>
+        <v>68071.13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>707426-73-CM26</t>
+          <t>3950-487-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7344,27 +7344,27 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7389,13 +7389,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3923.71</v>
+        <v>5197.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3950-637-CM26</t>
+          <t>1079689-141-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7450,13 +7450,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6285.93</v>
+        <v>26224.58</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>734-281-CM26</t>
+          <t>2151-119-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7511,13 +7511,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>40363.17</v>
+        <v>9671.219999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1692-329-CM26</t>
+          <t>3950-533-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7527,27 +7527,27 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>15365.56</v>
+        <v>12807.29</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1294237-30-CM26</t>
+          <t>734-209-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7633,13 +7633,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3061.11</v>
+        <v>37953.42</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3949-193-CM26</t>
+          <t>3949-161-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7694,13 +7694,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>13370.37</v>
+        <v>15921.07</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2151-165-CM26</t>
+          <t>3765-328-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7755,13 +7755,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8885.860000000001</v>
+        <v>11739.78</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>951405-160-CM26</t>
+          <t>3431-49-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7816,13 +7816,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>994.73</v>
+        <v>3746.8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3950-689-CM26</t>
+          <t>1692-258-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7832,12 +7832,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>13516.97</v>
+        <v>14139.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3765-438-CM26</t>
+          <t>1403-272-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>11630.34</v>
+        <v>394.89</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>418-1637-CM26</t>
+          <t>951405-100-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7999,13 +7999,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>37168.77</v>
+        <v>3599.14</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3951-117-CM26</t>
+          <t>3951-90-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8060,13 +8060,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12194.22</v>
+        <v>10333.02</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1079689-227-CM26</t>
+          <t>1079689-170-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8121,13 +8121,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>25126.3</v>
+        <v>22310.19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4778-358-CM26</t>
+          <t>4778-256-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8137,12 +8137,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>61371.32</v>
+        <v>68664.92999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>3431-104-CM26</t>
+          <t>3431-61-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4921.05</v>
+        <v>4811.55</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3950-848-CM26</t>
+          <t>707426-69-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8304,13 +8304,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>11535.62</v>
+        <v>16598.9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3950-783-CM26</t>
+          <t>707426-73-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8365,13 +8365,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5757.18</v>
+        <v>3923.71</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1692-392-CM26</t>
+          <t>3950-637-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8426,13 +8426,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>13541.06</v>
+        <v>6285.93</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2151-216-CM26</t>
+          <t>1692-329-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8442,27 +8442,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8487,13 +8487,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9290.809999999999</v>
+        <v>15365.56</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1274667-197-CM26</t>
+          <t>734-281-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8548,13 +8548,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>15045.04</v>
+        <v>40363.17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3949-241-CM26</t>
+          <t>3950-689-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8579,12 +8579,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8609,13 +8609,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>10562.72</v>
+        <v>13516.97</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>734-395-CM26</t>
+          <t>951405-160-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8670,13 +8670,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>37742.24</v>
+        <v>994.73</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1294237-39-CM26</t>
+          <t>2151-165-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4223.92</v>
+        <v>8885.860000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3765-530-CM26</t>
+          <t>3949-193-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8792,13 +8792,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>10448.04</v>
+        <v>13370.37</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>3431-109-CM26</t>
+          <t>1294237-30-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8853,28 +8853,28 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4120.16</v>
+        <v>3061.11</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>418-2073-CM26</t>
+          <t>3765-438-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8914,28 +8914,28 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>37775.93</v>
+        <v>11630.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3951-148-CM26</t>
+          <t>418-1637-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8945,12 +8945,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8975,28 +8975,28 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>12390.94</v>
+        <v>37168.77</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1079689-282-CM26</t>
+          <t>3951-117-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9036,28 +9036,28 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>24626.52</v>
+        <v>12194.22</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>4778-394-CM26</t>
+          <t>1079689-227-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9097,28 +9097,28 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>68759.23</v>
+        <v>25126.3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2151-258-CM26</t>
+          <t>4778-358-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9158,28 +9158,28 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>10038.52</v>
+        <v>61371.32</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1692-456-CM26</t>
+          <t>3431-104-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9219,28 +9219,28 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>15168.21</v>
+        <v>4921.05</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>734-483-CM26</t>
+          <t>3950-783-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9280,28 +9280,28 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>42471.7</v>
+        <v>5757.18</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1274667-257-CM26</t>
+          <t>3950-848-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9341,28 +9341,28 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>14598.07</v>
+        <v>11535.62</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3949-287-CM26</t>
+          <t>1692-392-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9402,28 +9402,28 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>16570.18</v>
+        <v>13541.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>655348-64-CM26</t>
+          <t>2151-216-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9463,28 +9463,28 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>389.28</v>
+        <v>9290.809999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3950-1047-CM26</t>
+          <t>1274667-197-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9524,28 +9524,28 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>14044.37</v>
+        <v>15045.04</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3765-626-CM26</t>
+          <t>3949-241-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9585,28 +9585,28 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12523.22</v>
+        <v>10562.72</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1079689-299-CM26</t>
+          <t>734-395-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9646,28 +9646,28 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>25990.94</v>
+        <v>37742.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3950-1008-CM26</t>
+          <t>1294237-39-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9707,28 +9707,28 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5449.75</v>
+        <v>4223.92</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>3950-1016-CM26</t>
+          <t>3765-530-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9768,28 +9768,28 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>346.28</v>
+        <v>10448.04</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3951-184-CM26</t>
+          <t>3431-109-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9829,13 +9829,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>12110.8</v>
+        <v>4120.16</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3431-126-CM26</t>
+          <t>418-2073-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9845,12 +9845,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9890,13 +9890,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5102.7</v>
+        <v>37775.93</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>951405-272-CM26</t>
+          <t>3951-148-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9906,27 +9906,27 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9951,13 +9951,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3809.52</v>
+        <v>12390.94</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>418-2399-CM26</t>
+          <t>1079689-282-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10012,13 +10012,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>36953.38</v>
+        <v>24626.52</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3949-329-CM26</t>
+          <t>4778-394-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10073,13 +10073,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13759.22</v>
+        <v>68759.23</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1274667-318-CM26</t>
+          <t>2151-258-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10134,6 +10134,982 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
+        <v>10038.52</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1692-456-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>15168.21</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>734-483-CM26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>42471.7</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1274667-257-CM26</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>14598.07</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>3949-287-CM26</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>16570.18</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>655348-64-CM26</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>61.980.150-4</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>389.28</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>3950-1047-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>14044.37</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1079689-299-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>25990.94</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3765-626-CM26</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>61.602.281-4</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>12523.22</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3950-1008-CM26</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>5449.75</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>3950-1016-CM26</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>346.28</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>3951-184-CM26</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>61.974.700-3</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Consultorio General Urbano Victor Domingo Silva</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>12110.8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3431-126-CM26</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>5102.7</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>951405-272-CM26</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>3809.52</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>418-2399-CM26</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>36953.38</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>3949-329-CM26</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>13759.22</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1274667-318-CM26</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="n">
         <v>14672.71</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M362"/>
+  <dimension ref="A1:M376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2594,7 +2594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3950-1108-CM25</t>
+          <t>3765-160-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3619.49</v>
+        <v>7057.81</v>
       </c>
     </row>
     <row r="35">
@@ -2789,7 +2789,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3765-160-CM25</t>
+          <t>3950-1108-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7057.81</v>
+        <v>3619.49</v>
       </c>
     </row>
     <row r="38">
@@ -3114,7 +3114,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3431-27-CM25</t>
+          <t>655348-13-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4882.58</v>
+        <v>1079.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>655348-13-CM25</t>
+          <t>3431-27-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1079.74</v>
+        <v>4882.58</v>
       </c>
     </row>
     <row r="44">
@@ -3374,7 +3374,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>868-49-CM25</t>
+          <t>868-48-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4184.81</v>
+        <v>2789.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>868-48-CM25</t>
+          <t>868-49-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2789.87</v>
+        <v>4184.81</v>
       </c>
     </row>
     <row r="48">
@@ -3634,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2151-107-CM25</t>
+          <t>1608-62-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7036.36</v>
+        <v>1010.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1608-61-CM25</t>
+          <t>2151-107-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3719,17 +3719,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1010.83</v>
+        <v>7036.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1608-62-CM25</t>
+          <t>1692-2425-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3784,17 +3784,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1010.83</v>
+        <v>11008.42</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1692-2425-CM25</t>
+          <t>1608-61-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11008.42</v>
+        <v>1010.83</v>
       </c>
     </row>
     <row r="54">
@@ -4544,7 +4544,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3950-3550-CM25</t>
+          <t>1691-1352-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10848.35</v>
+        <v>50299.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1691-1352-CM25</t>
+          <t>3950-3550-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4629,17 +4629,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>50299.17</v>
+        <v>10848.35</v>
       </c>
     </row>
     <row r="66">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3950-3721-CM25</t>
+          <t>1691-1647-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>10428.92</v>
+        <v>46699.45</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1691-1647-CM25</t>
+          <t>3950-3721-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>46699.45</v>
+        <v>10428.92</v>
       </c>
     </row>
     <row r="84">
@@ -5909,7 +5909,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3949-198-CM25</t>
+          <t>3765-372-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>12682.09</v>
+        <v>7954.21</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1692-2586-CM25</t>
+          <t>3949-198-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>11931.31</v>
+        <v>12682.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3765-372-CM25</t>
+          <t>1692-2586-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7954.21</v>
+        <v>11931.31</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3950-3798-CM25</t>
+          <t>734-605-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3890.89</v>
+        <v>33159.37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>734-605-CM25</t>
+          <t>3950-3798-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>33159.37</v>
+        <v>3890.89</v>
       </c>
     </row>
     <row r="90">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3950-3893-CM25</t>
+          <t>1691-1856-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10663.67</v>
+        <v>49324.62</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1691-1856-CM25</t>
+          <t>3950-3893-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6839,17 +6839,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>49324.62</v>
+        <v>10663.67</v>
       </c>
     </row>
     <row r="100">
@@ -7794,7 +7794,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1079689-232-CM25</t>
+          <t>951405-244-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>18110.87</v>
+        <v>511.21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>951405-244-CM25</t>
+          <t>1079689-232-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>511.21</v>
+        <v>18110.87</v>
       </c>
     </row>
     <row r="116">
@@ -8444,7 +8444,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3765-548-CM25</t>
+          <t>3325-87-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>8254.41</v>
+        <v>3150.04</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3325-87-CM25</t>
+          <t>3765-548-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3150.04</v>
+        <v>8254.41</v>
       </c>
     </row>
     <row r="126">
@@ -8639,7 +8639,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3431-142-CM25</t>
+          <t>418-2694-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3995.56</v>
+        <v>27787.29</v>
       </c>
     </row>
     <row r="128">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>418-2694-CM25</t>
+          <t>3431-142-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>27787.29</v>
+        <v>3995.56</v>
       </c>
     </row>
     <row r="130">
@@ -8899,7 +8899,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1079689-277-CM25</t>
+          <t>1403-4067-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>17828.72</v>
+        <v>519.48</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1403-4067-CM25</t>
+          <t>3950-4261-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>519.48</v>
+        <v>4564.89</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3950-4261-CM25</t>
+          <t>1079689-277-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9049,17 +9049,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4564.89</v>
+        <v>17828.72</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1686-18-CM25</t>
+          <t>3951-264-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2576.14</v>
+        <v>7959.24</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3951-264-CM25</t>
+          <t>1686-18-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7959.24</v>
+        <v>2576.14</v>
       </c>
     </row>
     <row r="136">
@@ -9614,7 +9614,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3765-638-CM25</t>
+          <t>3431-153-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7879.63</v>
+        <v>4732.75</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3431-153-CM25</t>
+          <t>734-951-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4732.75</v>
+        <v>27307.76</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>734-951-CM25</t>
+          <t>3765-638-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>27307.76</v>
+        <v>7879.63</v>
       </c>
     </row>
     <row r="145">
@@ -10654,7 +10654,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3765-709-CM25</t>
+          <t>1692-2873-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,13 +10713,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6639.32</v>
+        <v>10784.59</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1692-2873-CM25</t>
+          <t>3765-709-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>10784.59</v>
+        <v>6639.32</v>
       </c>
     </row>
     <row r="160">
@@ -11954,7 +11954,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2151-393-CM25</t>
+          <t>3431-174-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>7305.58</v>
+        <v>468.7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3431-174-CM25</t>
+          <t>734-1133-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>468.7</v>
+        <v>37052.62</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>734-1133-CM25</t>
+          <t>3949-399-CM25</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>37052.62</v>
+        <v>13347.7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3949-399-CM25</t>
+          <t>1692-2969-CM25</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>13347.7</v>
+        <v>12415.4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1692-2969-CM25</t>
+          <t>2151-393-CM25</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>12415.4</v>
+        <v>7305.58</v>
       </c>
     </row>
     <row r="183">
@@ -12604,7 +12604,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>697209-45-CM25</t>
+          <t>418-7259-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12624,17 +12624,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6850.56</v>
+        <v>34456.23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>3431-179-CM25</t>
+          <t>1079689-385-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3499.97</v>
+        <v>638.64</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1079689-385-CM25</t>
+          <t>3431-179-CM25</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,13 +12793,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>638.64</v>
+        <v>3499.97</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>418-7259-CM25</t>
+          <t>697209-45-CM25</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12819,17 +12819,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>34456.23</v>
+        <v>6850.56</v>
       </c>
     </row>
     <row r="192">
@@ -12929,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3951-384-CM25</t>
+          <t>1079689-397-CM25</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>9552.15</v>
+        <v>17932.22</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1079689-397-CM25</t>
+          <t>3951-384-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>17932.22</v>
+        <v>9552.15</v>
       </c>
     </row>
     <row r="195">
@@ -13254,7 +13254,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3950-4823-CM25</t>
+          <t>1079689-403-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>10681.94</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3951-397-CM25</t>
+          <t>3950-4823-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13339,17 +13339,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>123.19</v>
+        <v>10681.94</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1079689-403-CM25</t>
+          <t>3951-397-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,7 +13443,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>36.96</v>
+        <v>123.19</v>
       </c>
     </row>
     <row r="201">
@@ -13774,7 +13774,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1079689-427-CM25</t>
+          <t>734-1196-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>948.03</v>
+        <v>33958.17</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>734-1196-CM25</t>
+          <t>1079689-427-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>33958.17</v>
+        <v>948.03</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1692-3022-CM25</t>
+          <t>3765-918-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>11567.75</v>
+        <v>7078.21</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3765-918-CM25</t>
+          <t>1692-3022-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>7078.21</v>
+        <v>11567.75</v>
       </c>
     </row>
     <row r="210">
@@ -15074,7 +15074,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3950-82-CM26</t>
+          <t>3431-2-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15094,17 +15094,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3730.9</v>
+        <v>4816.24</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3431-2-CM26</t>
+          <t>3950-82-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15159,17 +15159,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,7 +15198,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4816.24</v>
+        <v>3730.9</v>
       </c>
     </row>
     <row r="228">
@@ -15984,7 +15984,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>734-43-CM26</t>
+          <t>3765-153-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16009,12 +16009,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>37444.17</v>
+        <v>11721.42</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1692-84-CM26</t>
+          <t>3949-53-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16074,12 +16074,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,13 +16108,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>14283.19</v>
+        <v>11785.91</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3765-153-CM26</t>
+          <t>1692-84-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16139,12 +16139,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>11721.42</v>
+        <v>14283.19</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3949-53-CM26</t>
+          <t>734-43-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,7 +16238,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>11785.91</v>
+        <v>37444.17</v>
       </c>
     </row>
     <row r="244">
@@ -16894,7 +16894,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3431-38-CM26</t>
+          <t>1692-163-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4969.56</v>
+        <v>11826.71</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2151-77-CM26</t>
+          <t>734-134-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>9559.09</v>
+        <v>34045.13</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>734-134-CM26</t>
+          <t>2151-77-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>34045.13</v>
+        <v>9559.09</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1692-163-CM26</t>
+          <t>3431-38-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>11826.71</v>
+        <v>4969.56</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3765-246-CM26</t>
+          <t>1294237-17-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>9928.450000000001</v>
+        <v>863.23</v>
       </c>
     </row>
     <row r="259">
@@ -17284,7 +17284,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1294237-17-CM26</t>
+          <t>3765-246-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>863.23</v>
+        <v>9928.450000000001</v>
       </c>
     </row>
     <row r="261">
@@ -17609,7 +17609,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1274667-138-CM26</t>
+          <t>4778-151-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17634,12 +17634,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17668,13 +17668,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>14671.92</v>
+        <v>68071.13</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>4778-151-CM26</t>
+          <t>1274667-138-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17699,12 +17699,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17733,7 +17733,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>68071.13</v>
+        <v>14671.92</v>
       </c>
     </row>
     <row r="267">
@@ -18064,7 +18064,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3431-49-CM26</t>
+          <t>3949-161-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3746.8</v>
+        <v>15921.07</v>
       </c>
     </row>
     <row r="273">
@@ -18194,7 +18194,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3949-161-CM26</t>
+          <t>3431-49-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>15921.07</v>
+        <v>3746.8</v>
       </c>
     </row>
     <row r="275">
@@ -18909,7 +18909,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1692-329-CM26</t>
+          <t>734-281-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18929,17 +18929,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>15365.56</v>
+        <v>40363.17</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>734-281-CM26</t>
+          <t>1692-329-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18994,17 +18994,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>40363.17</v>
+        <v>15365.56</v>
       </c>
     </row>
     <row r="287">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2151-216-CM26</t>
+          <t>1692-392-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>9290.809999999999</v>
+        <v>13541.06</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1692-392-CM26</t>
+          <t>2151-216-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>13541.06</v>
+        <v>9290.809999999999</v>
       </c>
     </row>
     <row r="302">
@@ -20079,7 +20079,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3949-241-CM26</t>
+          <t>1294237-39-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20138,7 +20138,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>10562.72</v>
+        <v>4223.92</v>
       </c>
     </row>
     <row r="304">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1294237-39-CM26</t>
+          <t>3949-241-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>4223.92</v>
+        <v>10562.72</v>
       </c>
     </row>
     <row r="306">
@@ -20859,7 +20859,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>655348-64-CM26</t>
+          <t>3949-287-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>389.28</v>
+        <v>16570.18</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>3949-287-CM26</t>
+          <t>1274667-257-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20949,12 +20949,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20983,13 +20983,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>16570.18</v>
+        <v>14598.07</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1274667-257-CM26</t>
+          <t>655348-64-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -21048,13 +21048,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>14598.07</v>
+        <v>389.28</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1079689-299-CM26</t>
+          <t>3950-1047-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21079,12 +21079,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21113,7 +21113,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>25990.94</v>
+        <v>14044.37</v>
       </c>
     </row>
     <row r="319">
@@ -21184,7 +21184,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>3950-1047-CM26</t>
+          <t>1079689-299-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>14044.37</v>
+        <v>25990.94</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3950-1008-CM26</t>
+          <t>3950-1016-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5449.75</v>
+        <v>346.28</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3950-1016-CM26</t>
+          <t>3950-1008-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21373,13 +21373,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>346.28</v>
+        <v>5449.75</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3951-184-CM26</t>
+          <t>3431-126-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21404,12 +21404,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>12110.8</v>
+        <v>5102.7</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3431-126-CM26</t>
+          <t>3951-184-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21503,7 +21503,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>5102.7</v>
+        <v>12110.8</v>
       </c>
     </row>
     <row r="325">
@@ -21704,7 +21704,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3950-1193-CM26</t>
+          <t>3950-1196-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -21763,13 +21763,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6395.2</v>
+        <v>13458.04</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>3950-1196-CM26</t>
+          <t>3950-1193-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>13458.04</v>
+        <v>6395.2</v>
       </c>
     </row>
     <row r="330">
@@ -22094,7 +22094,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>655348-73-CM26</t>
+          <t>1692-551-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1184.21</v>
+        <v>14035.92</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>418-2626-CM26</t>
+          <t>3949-329-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22184,12 +22184,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>38166.12</v>
+        <v>13759.22</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>3949-329-CM26</t>
+          <t>655348-73-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>13759.22</v>
+        <v>1184.21</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1692-551-CM26</t>
+          <t>418-2626-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>14035.92</v>
+        <v>38166.12</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>734-564-CM26</t>
+          <t>3765-721-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,13 +22413,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>43795.22</v>
+        <v>11789.62</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3765-721-CM26</t>
+          <t>734-564-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>11789.62</v>
+        <v>43795.22</v>
       </c>
     </row>
     <row r="340">
@@ -22679,7 +22679,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>951405-316-CM26</t>
+          <t>682-31-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.802.014-2</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2177.65</v>
+        <v>2155.46</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>682-31-CM26</t>
+          <t>951405-316-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22769,12 +22769,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.802.014-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2155.46</v>
+        <v>2177.65</v>
       </c>
     </row>
     <row r="345">
@@ -23199,7 +23199,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1079689-388-CM26</t>
+          <t>1692-630-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23224,12 +23224,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>211.67</v>
+        <v>14948.13</v>
       </c>
     </row>
     <row r="352">
@@ -23329,7 +23329,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1692-630-CM26</t>
+          <t>1079689-388-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23388,7 +23388,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>14948.13</v>
+        <v>211.67</v>
       </c>
     </row>
     <row r="354">
@@ -23459,7 +23459,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>3949-377-CM26</t>
+          <t>734-663-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23484,12 +23484,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>15524.23</v>
+        <v>36267.11</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>734-663-CM26</t>
+          <t>3949-377-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>36267.11</v>
+        <v>15524.23</v>
       </c>
     </row>
     <row r="357">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -23974,6 +23974,916 @@
       </c>
       <c r="M362" s="2" t="n">
         <v>5864.65</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1092-116-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>1362.33</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>3950-1551-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>13100.57</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>4778-694-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>65841.33</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>734-748-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>37771.05</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1692-728-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>13082.16</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>655348-87-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>61.980.150-4</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>364.73</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>3949-420-CM26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>61.974.500-0</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>14378.36</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2151-404-CM26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="n">
+        <v>8542.719999999999</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>1274667-397-CM26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="n">
+        <v>13707.79</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>1079689-447-CM26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="n">
+        <v>135.44</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>3950-1613-CM26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="n">
+        <v>5321.79</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>3765-893-CM26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>61.602.281-4</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="n">
+        <v>10619.68</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>418-3432-CM26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="n">
+        <v>36186.48</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>951405-357-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>3770.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M378"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2724,7 +2724,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3765-160-CM25</t>
+          <t>1079689-61-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7057.81</v>
+        <v>16735.14</v>
       </c>
     </row>
     <row r="37">
@@ -2919,7 +2919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3950-1108-CM25</t>
+          <t>3765-160-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2939,17 +2939,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3619.49</v>
+        <v>7057.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079689-61-CM25</t>
+          <t>3950-1108-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16735.14</v>
+        <v>3619.49</v>
       </c>
     </row>
     <row r="41">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1608-61-CM25</t>
+          <t>2151-107-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1010.83</v>
+        <v>7036.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2151-107-CM25</t>
+          <t>1692-2425-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7036.36</v>
+        <v>11008.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1692-2425-CM25</t>
+          <t>1608-61-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>11008.42</v>
+        <v>1010.83</v>
       </c>
     </row>
     <row r="56">
@@ -4934,7 +4934,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3765-305-CM25</t>
+          <t>3765-297-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>406.78</v>
+        <v>7728.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3765-297-CM25</t>
+          <t>3765-305-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7728.74</v>
+        <v>406.78</v>
       </c>
     </row>
     <row r="72">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3950-3798-CM25</t>
+          <t>734-605-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3890.89</v>
+        <v>33159.37</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>734-605-CM25</t>
+          <t>3950-3798-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6319,17 +6319,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>33159.37</v>
+        <v>3890.89</v>
       </c>
     </row>
     <row r="92">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3765-548-CM25</t>
+          <t>734-820-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>8254.41</v>
+        <v>36793.21</v>
       </c>
     </row>
     <row r="126">
@@ -8639,7 +8639,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>734-820-CM25</t>
+          <t>3765-548-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>36793.21</v>
+        <v>8254.41</v>
       </c>
     </row>
     <row r="128">
@@ -9029,7 +9029,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3950-4261-CM25</t>
+          <t>1403-4067-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9049,17 +9049,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>4564.89</v>
+        <v>519.48</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1403-4067-CM25</t>
+          <t>3950-4261-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,7 +9153,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>519.48</v>
+        <v>4564.89</v>
       </c>
     </row>
     <row r="135">
@@ -9614,7 +9614,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1079689-291-CM25</t>
+          <t>2151-322-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>17825.14</v>
+        <v>7321.89</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2151-322-CM25</t>
+          <t>1079689-291-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7321.89</v>
+        <v>17825.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3765-638-CM25</t>
+          <t>3431-153-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>7879.63</v>
+        <v>4732.75</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>3431-153-CM25</t>
+          <t>734-951-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4732.75</v>
+        <v>27307.76</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>734-951-CM25</t>
+          <t>3765-638-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>27307.76</v>
+        <v>7879.63</v>
       </c>
     </row>
     <row r="147">
@@ -11044,7 +11044,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1405-91-CM25</t>
+          <t>3949-379-CM25</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>60.511.113-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CAPITÁN PRAT</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1285.13</v>
+        <v>11810.09</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3949-379-CM25</t>
+          <t>1405-91-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>60.511.113-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CAPITÁN PRAT</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>11810.09</v>
+        <v>1285.13</v>
       </c>
     </row>
     <row r="166">
@@ -11889,7 +11889,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>951405-370-CM25</t>
+          <t>1154-53-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11909,17 +11909,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3827.18</v>
+        <v>298.67</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>951405-367-CM25</t>
+          <t>951405-370-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>12611.07</v>
+        <v>3827.18</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1154-53-CM25</t>
+          <t>951405-367-CM25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12039,17 +12039,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12078,7 +12078,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>298.67</v>
+        <v>12611.07</v>
       </c>
     </row>
     <row r="180">
@@ -16114,7 +16114,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1692-84-CM26</t>
+          <t>3949-53-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16139,12 +16139,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -16173,13 +16173,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>14283.19</v>
+        <v>11785.91</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3949-53-CM26</t>
+          <t>3765-153-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>11785.91</v>
+        <v>11721.42</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3765-153-CM26</t>
+          <t>1692-84-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>11721.42</v>
+        <v>14283.19</v>
       </c>
     </row>
     <row r="245">
@@ -17024,7 +17024,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1692-163-CM26</t>
+          <t>734-134-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>11826.71</v>
+        <v>34045.13</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>734-134-CM26</t>
+          <t>3431-38-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>34045.13</v>
+        <v>4969.56</v>
       </c>
     </row>
     <row r="258">
@@ -17219,7 +17219,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3431-38-CM26</t>
+          <t>1692-163-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,7 +17278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4969.56</v>
+        <v>11826.71</v>
       </c>
     </row>
     <row r="260">
@@ -17349,7 +17349,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3949-116-CM26</t>
+          <t>3765-246-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>8203.540000000001</v>
+        <v>9928.450000000001</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3765-246-CM26</t>
+          <t>3949-116-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17439,12 +17439,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,7 +17473,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>9928.450000000001</v>
+        <v>8203.540000000001</v>
       </c>
     </row>
     <row r="263">
@@ -17934,7 +17934,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3950-533-CM26</t>
+          <t>1079689-141-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>12807.29</v>
+        <v>26224.58</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2151-119-CM26</t>
+          <t>3950-487-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18019,17 +18019,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>9671.219999999999</v>
+        <v>5197.91</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1079689-141-CM26</t>
+          <t>2151-119-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>26224.58</v>
+        <v>9671.219999999999</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3950-487-CM26</t>
+          <t>3950-533-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5197.91</v>
+        <v>12807.29</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1692-258-CM26</t>
+          <t>3431-49-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>14139.2</v>
+        <v>3746.8</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3431-49-CM26</t>
+          <t>3949-161-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3746.8</v>
+        <v>15921.07</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3949-161-CM26</t>
+          <t>3765-328-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>15921.07</v>
+        <v>11739.78</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3765-328-CM26</t>
+          <t>1692-258-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>11739.78</v>
+        <v>14139.2</v>
       </c>
     </row>
     <row r="278">
@@ -18779,7 +18779,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3431-61-CM26</t>
+          <t>707426-69-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.101.085-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4811.55</v>
+        <v>16598.9</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>707426-69-CM26</t>
+          <t>3431-61-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>16598.9</v>
+        <v>4811.55</v>
       </c>
     </row>
     <row r="285">
@@ -19364,7 +19364,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3949-193-CM26</t>
+          <t>1294237-30-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>13370.37</v>
+        <v>3061.11</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1294237-30-CM26</t>
+          <t>3949-193-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19488,7 +19488,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3061.11</v>
+        <v>13370.37</v>
       </c>
     </row>
     <row r="294">
@@ -20144,7 +20144,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1294237-39-CM26</t>
+          <t>734-395-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>4223.92</v>
+        <v>37742.24</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>734-395-CM26</t>
+          <t>1294237-39-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>37742.24</v>
+        <v>4223.92</v>
       </c>
     </row>
     <row r="306">
@@ -20989,7 +20989,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1274667-257-CM26</t>
+          <t>655348-64-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -21048,13 +21048,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>14598.07</v>
+        <v>389.28</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>655348-64-CM26</t>
+          <t>3949-287-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -21079,12 +21079,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -21113,13 +21113,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>389.28</v>
+        <v>16570.18</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3949-287-CM26</t>
+          <t>1274667-257-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,13 +21178,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>16570.18</v>
+        <v>14598.07</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>3950-1047-CM26</t>
+          <t>3765-626-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>14044.37</v>
+        <v>12523.22</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3765-626-CM26</t>
+          <t>1079689-299-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21274,12 +21274,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21308,13 +21308,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>12523.22</v>
+        <v>25990.94</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1079689-299-CM26</t>
+          <t>3950-1047-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21373,7 +21373,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>25990.94</v>
+        <v>14044.37</v>
       </c>
     </row>
     <row r="323">
@@ -22354,7 +22354,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>655348-73-CM26</t>
+          <t>418-2626-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.980.150-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,13 +22413,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1184.21</v>
+        <v>38166.12</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>418-2626-CM26</t>
+          <t>655348-73-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.150-4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22478,7 +22478,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>38166.12</v>
+        <v>1184.21</v>
       </c>
     </row>
     <row r="340">
@@ -22809,7 +22809,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>682-31-CM26</t>
+          <t>951405-316-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>61.802.014-2</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22868,13 +22868,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2155.46</v>
+        <v>2177.65</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>951405-316-CM26</t>
+          <t>682-31-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22899,12 +22899,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.802.014-2</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22933,7 +22933,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2177.65</v>
+        <v>2155.46</v>
       </c>
     </row>
     <row r="347">
@@ -23134,7 +23134,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>4778-566-CM26</t>
+          <t>2151-352-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23154,17 +23154,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>68082.39</v>
+        <v>9433.42</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2151-352-CM26</t>
+          <t>4778-566-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23219,17 +23219,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>9433.42</v>
+        <v>68082.39</v>
       </c>
     </row>
     <row r="352">
@@ -25014,6 +25014,136 @@
       </c>
       <c r="M378" s="2" t="n">
         <v>3770.6</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>3950-1682-CM26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="n">
+        <v>12207.57</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>1079689-450-CM26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="n">
+        <v>23669.03</v>
       </c>
     </row>
   </sheetData>
